--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>

--- a/TransactionsLatestCAS.xlsx
+++ b/TransactionsLatestCAS.xlsx
@@ -11175,7 +11175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -11188,7 +11188,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
+          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -11201,7 +11201,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HDFC Manufacturing Fund Direct Growth</t>
+          <t>quant Infrastructure Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bandhan ELSS Tax saver Fund-Regular Plan-Growth</t>
+          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -11227,7 +11227,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
+          <t>HDFC ELSS Tax saver - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -11240,7 +11240,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
+          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -11253,7 +11253,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
+          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -11266,7 +11266,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SBI Automotive Opportunities Fund - Direct Growth</t>
+          <t>HDFC Manufacturing Fund Direct Growth</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -11279,7 +11279,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bandhan Value Fund-Direct Plan-Growth ( Formerly Known as Bandhan Sterling Value Fund-Direct Plan-Growth)</t>
+          <t>NIPPON INDIA GROWTH MID CAP FUND - DIRECT GROWTH PLAN GROWTH OPTION (Non Demat)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>quant Large Cap Fund - Direct Plan - Growth (Non Demat)</t>
+          <t>Motilal Oswal BSE Enhanced Value Index Fund - Direct Growth (Non Demat)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -11305,7 +11305,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mahindra Manulife Small Cap Fund - Direct - Growth</t>
+          <t>DSP Large Cap Fund - Regular Plan - Growth</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
